--- a/Trade-Monitoring-Source-Data-Checklist.xlsx
+++ b/Trade-Monitoring-Source-Data-Checklist.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Not sourced" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 Field checklist'!$A$4:$O$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 Field checklist'!$A$4:$O$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -662,7 +662,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>298 fields in total. 187 have to be sourced from the bank and are listed on '3 Field checklist'. The remaining 111 are produced by the surveillance platform itself or computed by the warehouse — they are on '5 Not sourced' so that nobody spends time hunting for them.</t>
+          <t>300 fields in total. 189 have to be sourced from the bank and are listed on '3 Field checklist'. The remaining 111 are produced by the surveillance platform itself or computed by the warehouse — they are on '5 Not sourced' so that nobody spends time hunting for them.</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>6</v>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E18" s="19" t="n">
         <v>156</v>
@@ -1261,7 +1261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O192"/>
+  <dimension ref="A1:O194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1284,7 +1284,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Field checklist — 187 fields to source</t>
+          <t>Field checklist — 189 fields to source</t>
         </is>
       </c>
     </row>
@@ -8957,37 +8957,37 @@
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>Business date</t>
+          <t>Client revenue USD</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>business_date</t>
+          <t>client_revenue_usd</t>
         </is>
       </c>
       <c r="E153" s="26" t="inlineStr">
         <is>
-          <t>FACT_PNL_DAILY</t>
+          <t>FACT_TRADE</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="G153" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>DECIMAL(18,3)</t>
+        </is>
+      </c>
+      <c r="G153" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>0.214</t>
         </is>
       </c>
       <c r="I153" s="11" t="inlineStr">
         <is>
-          <t>P&amp;L date.</t>
+          <t>Dealing revenue earned on the ticket — the spread the desk captured on the deal, before any result from holding the risk it took on. USD thousands.</t>
         </is>
       </c>
       <c r="J153" s="24" t="inlineStr"/>
@@ -9008,37 +9008,37 @@
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Daily P&amp;L USD</t>
+          <t>Total revenue USD</t>
         </is>
       </c>
       <c r="D154" s="23" t="inlineStr">
         <is>
-          <t>daily_pnl_usd</t>
+          <t>total_revenue_usd</t>
         </is>
       </c>
       <c r="E154" s="22" t="inlineStr">
         <is>
-          <t>FACT_PNL_DAILY</t>
+          <t>FACT_TRADE</t>
         </is>
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2)</t>
-        </is>
-      </c>
-      <c r="G154" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>DECIMAL(18,3)</t>
+        </is>
+      </c>
+      <c r="G154" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="H154" s="15" t="inlineStr">
         <is>
-          <t>218.40</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>Signed daily P&amp;L, USD thousands.</t>
+          <t>Client revenue plus the result of holding the risk the deal took on. The figure the Trade Activity P&amp;L view sums. USD thousands.</t>
         </is>
       </c>
       <c r="J154" s="24" t="inlineStr"/>
@@ -9059,12 +9059,12 @@
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>Trader ID</t>
+          <t>Business date</t>
         </is>
       </c>
       <c r="D155" s="27" t="inlineStr">
         <is>
-          <t>trader_id</t>
+          <t>business_date</t>
         </is>
       </c>
       <c r="E155" s="26" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="F155" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="G155" s="13" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>T54</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I155" s="11" t="inlineStr">
         <is>
-          <t>Trader.</t>
+          <t>P&amp;L date.</t>
         </is>
       </c>
       <c r="J155" s="24" t="inlineStr"/>
@@ -9110,12 +9110,12 @@
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Unexplained P&amp;L USD</t>
+          <t>Daily P&amp;L USD</t>
         </is>
       </c>
       <c r="D156" s="23" t="inlineStr">
         <is>
-          <t>unexplained_pnl_usd</t>
+          <t>daily_pnl_usd</t>
         </is>
       </c>
       <c r="E156" s="22" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="H156" s="15" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>218.40</t>
         </is>
       </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>P&amp;L not attributable to known risk factors.</t>
+          <t>Signed daily P&amp;L, USD thousands.</t>
         </is>
       </c>
       <c r="J156" s="24" t="inlineStr"/>
@@ -9161,12 +9161,12 @@
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>Day one P&amp;L USD</t>
+          <t>Trader ID</t>
         </is>
       </c>
       <c r="D157" s="27" t="inlineStr">
         <is>
-          <t>day_one_pnl_usd</t>
+          <t>trader_id</t>
         </is>
       </c>
       <c r="E157" s="26" t="inlineStr">
@@ -9176,22 +9176,22 @@
       </c>
       <c r="F157" s="11" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2)</t>
-        </is>
-      </c>
-      <c r="G157" s="17" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="G157" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>63.00</t>
+          <t>T54</t>
         </is>
       </c>
       <c r="I157" s="11" t="inlineStr">
         <is>
-          <t>Day-one P&amp;L on model-priced deals booked today.</t>
+          <t>Trader.</t>
         </is>
       </c>
       <c r="J157" s="24" t="inlineStr"/>
@@ -9212,12 +9212,12 @@
       </c>
       <c r="C158" s="15" t="inlineStr">
         <is>
-          <t>IPV adjustment USD</t>
+          <t>Unexplained P&amp;L USD</t>
         </is>
       </c>
       <c r="D158" s="23" t="inlineStr">
         <is>
-          <t>ipv_adjustment_usd</t>
+          <t>unexplained_pnl_usd</t>
         </is>
       </c>
       <c r="E158" s="22" t="inlineStr">
@@ -9230,19 +9230,19 @@
           <t>DECIMAL(18,2)</t>
         </is>
       </c>
-      <c r="G158" s="22" t="inlineStr">
-        <is>
-          <t>Optional</t>
+      <c r="G158" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>Independent price verification adjustment applied.</t>
+          <t>P&amp;L not attributable to known risk factors.</t>
         </is>
       </c>
       <c r="J158" s="24" t="inlineStr"/>
@@ -9258,42 +9258,42 @@
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Risk engine</t>
+          <t>Product control &amp; finance</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>Business date</t>
+          <t>Day one P&amp;L USD</t>
         </is>
       </c>
       <c r="D159" s="27" t="inlineStr">
         <is>
-          <t>business_date</t>
+          <t>day_one_pnl_usd</t>
         </is>
       </c>
       <c r="E159" s="26" t="inlineStr">
         <is>
-          <t>FACT_POSITION</t>
+          <t>FACT_PNL_DAILY</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="G159" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>DECIMAL(18,2)</t>
+        </is>
+      </c>
+      <c r="G159" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>63.00</t>
         </is>
       </c>
       <c r="I159" s="11" t="inlineStr">
         <is>
-          <t>Position date.</t>
+          <t>Day-one P&amp;L on model-priced deals booked today.</t>
         </is>
       </c>
       <c r="J159" s="24" t="inlineStr"/>
@@ -9309,42 +9309,42 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Risk engine</t>
+          <t>Product control &amp; finance</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
         <is>
-          <t>Gross position USD</t>
+          <t>IPV adjustment USD</t>
         </is>
       </c>
       <c r="D160" s="23" t="inlineStr">
         <is>
-          <t>gross_position_usd</t>
+          <t>ipv_adjustment_usd</t>
         </is>
       </c>
       <c r="E160" s="22" t="inlineStr">
         <is>
-          <t>FACT_POSITION</t>
+          <t>FACT_PNL_DAILY</t>
         </is>
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
-          <t>DECIMAL(18,6)</t>
-        </is>
-      </c>
-      <c r="G160" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>DECIMAL(18,2)</t>
+        </is>
+      </c>
+      <c r="G160" s="22" t="inlineStr">
+        <is>
+          <t>Optional</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>688.200000</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>Gross position, USD millions.</t>
+          <t>Independent price verification adjustment applied.</t>
         </is>
       </c>
       <c r="J160" s="24" t="inlineStr"/>
@@ -9365,12 +9365,12 @@
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>Instrument ID</t>
+          <t>Business date</t>
         </is>
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>instrument_id</t>
+          <t>business_date</t>
         </is>
       </c>
       <c r="E161" s="26" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="G161" s="13" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>SGD IRS</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="I161" s="11" t="inlineStr">
         <is>
-          <t>Instrument or risk bucket.</t>
+          <t>Position date.</t>
         </is>
       </c>
       <c r="J161" s="24" t="inlineStr"/>
@@ -9416,12 +9416,12 @@
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Net position USD</t>
+          <t>Gross position USD</t>
         </is>
       </c>
       <c r="D162" s="23" t="inlineStr">
         <is>
-          <t>net_position_usd</t>
+          <t>gross_position_usd</t>
         </is>
       </c>
       <c r="E162" s="22" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>412.500000</t>
+          <t>688.200000</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>Net position, USD millions, signed.</t>
+          <t>Gross position, USD millions.</t>
         </is>
       </c>
       <c r="J162" s="24" t="inlineStr"/>
@@ -9467,12 +9467,12 @@
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>Snapshot timestamp</t>
+          <t>Instrument ID</t>
         </is>
       </c>
       <c r="D163" s="27" t="inlineStr">
         <is>
-          <t>snapshot_timestamp</t>
+          <t>instrument_id</t>
         </is>
       </c>
       <c r="E163" s="26" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="F163" s="11" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6) WITH TIME ZONE</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="G163" s="13" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>2025-08-04T18:00:00+08:00</t>
+          <t>SGD IRS</t>
         </is>
       </c>
       <c r="I163" s="11" t="inlineStr">
         <is>
-          <t>Time of the snapshot.</t>
+          <t>Instrument or risk bucket.</t>
         </is>
       </c>
       <c r="J163" s="24" t="inlineStr"/>
@@ -9518,12 +9518,12 @@
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Snapshot type</t>
+          <t>Net position USD</t>
         </is>
       </c>
       <c r="D164" s="23" t="inlineStr">
         <is>
-          <t>snapshot_type</t>
+          <t>net_position_usd</t>
         </is>
       </c>
       <c r="E164" s="22" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="F164" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
+          <t>DECIMAL(18,6)</t>
         </is>
       </c>
       <c r="G164" s="13" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
-          <t>EOD</t>
+          <t>412.500000</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>Intraday snapshot or end of day.</t>
+          <t>Net position, USD millions, signed.</t>
         </is>
       </c>
       <c r="J164" s="24" t="inlineStr"/>
@@ -9569,12 +9569,12 @@
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>Trader ID</t>
+          <t>Snapshot timestamp</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>trader_id</t>
+          <t>snapshot_timestamp</t>
         </is>
       </c>
       <c r="E165" s="26" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="F165" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>TIMESTAMP(6) WITH TIME ZONE</t>
         </is>
       </c>
       <c r="G165" s="13" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>T54</t>
+          <t>2025-08-04T18:00:00+08:00</t>
         </is>
       </c>
       <c r="I165" s="11" t="inlineStr">
         <is>
-          <t>Position holder.</t>
+          <t>Time of the snapshot.</t>
         </is>
       </c>
       <c r="J165" s="24" t="inlineStr"/>
@@ -9615,27 +9615,27 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Settlement &amp; confirmations</t>
+          <t>Risk engine</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>SSI changed</t>
+          <t>Snapshot type</t>
         </is>
       </c>
       <c r="D166" s="23" t="inlineStr">
         <is>
-          <t>ssi_changed</t>
+          <t>snapshot_type</t>
         </is>
       </c>
       <c r="E166" s="22" t="inlineStr">
         <is>
-          <t>FACT_TRADE</t>
+          <t>FACT_POSITION</t>
         </is>
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(10)</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>EOD</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>Standing settlement instruction was changed on this deal after booking.</t>
+          <t>Intraday snapshot or end of day.</t>
         </is>
       </c>
       <c r="J166" s="24" t="inlineStr"/>
@@ -9666,42 +9666,42 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Settlement &amp; confirmations</t>
+          <t>Risk engine</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>Collateral type</t>
+          <t>Trader ID</t>
         </is>
       </c>
       <c r="D167" s="27" t="inlineStr">
         <is>
-          <t>collateral_type</t>
+          <t>trader_id</t>
         </is>
       </c>
       <c r="E167" s="26" t="inlineStr">
         <is>
-          <t>DIM_INSTRUMENT</t>
+          <t>FACT_POSITION</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(10)</t>
-        </is>
-      </c>
-      <c r="G167" s="17" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="G167" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>T54</t>
         </is>
       </c>
       <c r="I167" s="11" t="inlineStr">
         <is>
-          <t>Collateral basket / eligibility code.</t>
+          <t>Position holder.</t>
         </is>
       </c>
       <c r="J167" s="24" t="inlineStr"/>
@@ -9722,22 +9722,22 @@
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Beneficiary account</t>
+          <t>SSI changed</t>
         </is>
       </c>
       <c r="D168" s="23" t="inlineStr">
         <is>
-          <t>beneficiary_account</t>
+          <t>ssi_changed</t>
         </is>
       </c>
       <c r="E168" s="22" t="inlineStr">
         <is>
-          <t>FACT_SETTLEMENT</t>
+          <t>FACT_TRADE</t>
         </is>
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR(40)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>MY89 1234 5678 9012</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>Account credited.</t>
+          <t>Standing settlement instruction was changed on this deal after booking.</t>
         </is>
       </c>
       <c r="J168" s="24" t="inlineStr"/>
@@ -9773,37 +9773,37 @@
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>Beneficiary country</t>
+          <t>Collateral type</t>
         </is>
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>beneficiary_country</t>
+          <t>collateral_type</t>
         </is>
       </c>
       <c r="E169" s="26" t="inlineStr">
         <is>
-          <t>FACT_SETTLEMENT</t>
+          <t>DIM_INSTRUMENT</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(40)</t>
-        </is>
-      </c>
-      <c r="G169" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="G169" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="I169" s="11" t="inlineStr">
         <is>
-          <t>Country of the receiving account.</t>
+          <t>Collateral basket / eligibility code.</t>
         </is>
       </c>
       <c r="J169" s="24" t="inlineStr"/>
@@ -9824,12 +9824,12 @@
       </c>
       <c r="C170" s="15" t="inlineStr">
         <is>
-          <t>Settlement amount</t>
+          <t>Beneficiary account</t>
         </is>
       </c>
       <c r="D170" s="23" t="inlineStr">
         <is>
-          <t>settlement_amount</t>
+          <t>beneficiary_account</t>
         </is>
       </c>
       <c r="E170" s="22" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2)</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>18300000.00</t>
+          <t>MY89 1234 5678 9012</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>Amount settled.</t>
+          <t>Account credited.</t>
         </is>
       </c>
       <c r="J170" s="24" t="inlineStr"/>
@@ -9875,12 +9875,12 @@
       </c>
       <c r="C171" s="11" t="inlineStr">
         <is>
-          <t>Settlement currency</t>
+          <t>Beneficiary country</t>
         </is>
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>settlement_ccy</t>
+          <t>beneficiary_country</t>
         </is>
       </c>
       <c r="E171" s="26" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="F171" s="11" t="inlineStr">
         <is>
-          <t>CHAR(3)</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="G171" s="13" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="I171" s="11" t="inlineStr">
         <is>
-          <t>Settlement currency.</t>
+          <t>Country of the receiving account.</t>
         </is>
       </c>
       <c r="J171" s="24" t="inlineStr"/>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="C172" s="15" t="inlineStr">
         <is>
-          <t>Settlement leg</t>
+          <t>Settlement amount</t>
         </is>
       </c>
       <c r="D172" s="23" t="inlineStr">
         <is>
-          <t>settlement_leg</t>
+          <t>settlement_amount</t>
         </is>
       </c>
       <c r="E172" s="22" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F172" s="15" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
+          <t>DECIMAL(18,2)</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="H172" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18300000.00</t>
         </is>
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>Leg number.</t>
+          <t>Amount settled.</t>
         </is>
       </c>
       <c r="J172" s="24" t="inlineStr"/>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="C173" s="11" t="inlineStr">
         <is>
-          <t>Settlement status</t>
+          <t>Settlement currency</t>
         </is>
       </c>
       <c r="D173" s="27" t="inlineStr">
         <is>
-          <t>settlement_status</t>
+          <t>settlement_ccy</t>
         </is>
       </c>
       <c r="E173" s="26" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="F173" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>CHAR(3)</t>
         </is>
       </c>
       <c r="G173" s="13" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Settled</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="I173" s="11" t="inlineStr">
         <is>
-          <t>Status of the payment.</t>
+          <t>Settlement currency.</t>
         </is>
       </c>
       <c r="J173" s="24" t="inlineStr"/>
@@ -10028,12 +10028,12 @@
       </c>
       <c r="C174" s="15" t="inlineStr">
         <is>
-          <t>SSI changed after booking</t>
+          <t>Settlement leg</t>
         </is>
       </c>
       <c r="D174" s="23" t="inlineStr">
         <is>
-          <t>ssi_changed_after_booking</t>
+          <t>settlement_leg</t>
         </is>
       </c>
       <c r="E174" s="22" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="F174" s="15" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>SMALLINT</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="H174" s="15" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>The SSI was altered between booking and settlement.</t>
+          <t>Leg number.</t>
         </is>
       </c>
       <c r="J174" s="24" t="inlineStr"/>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="C175" s="11" t="inlineStr">
         <is>
-          <t>SSI ID</t>
+          <t>Settlement status</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>ssi_id</t>
+          <t>settlement_status</t>
         </is>
       </c>
       <c r="E175" s="26" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="F175" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="G175" s="13" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>SSI-004412</t>
+          <t>Settled</t>
         </is>
       </c>
       <c r="I175" s="11" t="inlineStr">
         <is>
-          <t>Standing settlement instruction applied.</t>
+          <t>Status of the payment.</t>
         </is>
       </c>
       <c r="J175" s="24" t="inlineStr"/>
@@ -10130,12 +10130,12 @@
       </c>
       <c r="C176" s="15" t="inlineStr">
         <is>
-          <t>Trade ID</t>
+          <t>SSI changed after booking</t>
         </is>
       </c>
       <c r="D176" s="23" t="inlineStr">
         <is>
-          <t>trade_id</t>
+          <t>ssi_changed_after_booking</t>
         </is>
       </c>
       <c r="E176" s="22" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="F176" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr">
@@ -10155,12 +10155,12 @@
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
-          <t>TRD-051386</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>Deal being settled.</t>
+          <t>The SSI was altered between booking and settlement.</t>
         </is>
       </c>
       <c r="J176" s="24" t="inlineStr"/>
@@ -10181,22 +10181,22 @@
       </c>
       <c r="C177" s="11" t="inlineStr">
         <is>
-          <t>Beneficiary account</t>
+          <t>SSI ID</t>
         </is>
       </c>
       <c r="D177" s="27" t="inlineStr">
         <is>
-          <t>beneficiary_account</t>
+          <t>ssi_id</t>
         </is>
       </c>
       <c r="E177" s="26" t="inlineStr">
         <is>
-          <t>REF_SSI</t>
+          <t>FACT_SETTLEMENT</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(40)</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="G177" s="13" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>MY89 1234 5678 9012</t>
+          <t>SSI-004412</t>
         </is>
       </c>
       <c r="I177" s="11" t="inlineStr">
         <is>
-          <t>Account details.</t>
+          <t>Standing settlement instruction applied.</t>
         </is>
       </c>
       <c r="J177" s="24" t="inlineStr"/>
@@ -10232,22 +10232,22 @@
       </c>
       <c r="C178" s="15" t="inlineStr">
         <is>
-          <t>Beneficiary country</t>
+          <t>Trade ID</t>
         </is>
       </c>
       <c r="D178" s="23" t="inlineStr">
         <is>
-          <t>beneficiary_country</t>
+          <t>trade_id</t>
         </is>
       </c>
       <c r="E178" s="22" t="inlineStr">
         <is>
-          <t>REF_SSI</t>
+          <t>FACT_SETTLEMENT</t>
         </is>
       </c>
       <c r="F178" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR(40)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="H178" s="15" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>TRD-051386</t>
         </is>
       </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>Country of the account.</t>
+          <t>Deal being settled.</t>
         </is>
       </c>
       <c r="J178" s="24" t="inlineStr"/>
@@ -10283,12 +10283,12 @@
       </c>
       <c r="C179" s="11" t="inlineStr">
         <is>
-          <t>Changed by</t>
+          <t>Beneficiary account</t>
         </is>
       </c>
       <c r="D179" s="27" t="inlineStr">
         <is>
-          <t>changed_by</t>
+          <t>beneficiary_account</t>
         </is>
       </c>
       <c r="E179" s="26" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="F179" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="G179" s="13" t="inlineStr">
@@ -10308,12 +10308,12 @@
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>OPS0192</t>
+          <t>MY89 1234 5678 9012</t>
         </is>
       </c>
       <c r="I179" s="11" t="inlineStr">
         <is>
-          <t>Who created or amended the SSI.</t>
+          <t>Account details.</t>
         </is>
       </c>
       <c r="J179" s="24" t="inlineStr"/>
@@ -10334,12 +10334,12 @@
       </c>
       <c r="C180" s="15" t="inlineStr">
         <is>
-          <t>Counterparty ID</t>
+          <t>Beneficiary country</t>
         </is>
       </c>
       <c r="D180" s="23" t="inlineStr">
         <is>
-          <t>counterparty_id</t>
+          <t>beneficiary_country</t>
         </is>
       </c>
       <c r="E180" s="22" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
-          <t>CHAR(20)</t>
+          <t>VARCHAR(40)</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="H180" s="15" t="inlineStr">
         <is>
-          <t>5493001KJTIIGC8Y1R12</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>Counterparty the SSI belongs to.</t>
+          <t>Country of the account.</t>
         </is>
       </c>
       <c r="J180" s="24" t="inlineStr"/>
@@ -10385,12 +10385,12 @@
       </c>
       <c r="C181" s="11" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Changed by</t>
         </is>
       </c>
       <c r="D181" s="27" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>changed_by</t>
         </is>
       </c>
       <c r="E181" s="26" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="F181" s="11" t="inlineStr">
         <is>
-          <t>CHAR(3)</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="G181" s="13" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>OPS0192</t>
         </is>
       </c>
       <c r="I181" s="11" t="inlineStr">
         <is>
-          <t>Currency the SSI applies to.</t>
+          <t>Who created or amended the SSI.</t>
         </is>
       </c>
       <c r="J181" s="24" t="inlineStr"/>
@@ -10436,12 +10436,12 @@
       </c>
       <c r="C182" s="15" t="inlineStr">
         <is>
-          <t>Is approved</t>
+          <t>Counterparty ID</t>
         </is>
       </c>
       <c r="D182" s="23" t="inlineStr">
         <is>
-          <t>is_approved</t>
+          <t>counterparty_id</t>
         </is>
       </c>
       <c r="E182" s="22" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="F182" s="15" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>CHAR(20)</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>5493001KJTIIGC8Y1R12</t>
         </is>
       </c>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>The change went through four-eyes approval.</t>
+          <t>Counterparty the SSI belongs to.</t>
         </is>
       </c>
       <c r="J182" s="24" t="inlineStr"/>
@@ -10487,12 +10487,12 @@
       </c>
       <c r="C183" s="11" t="inlineStr">
         <is>
-          <t>SSI ID</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>ssi_id</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="E183" s="26" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="F183" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>CHAR(3)</t>
         </is>
       </c>
       <c r="G183" s="13" t="inlineStr">
@@ -10512,12 +10512,12 @@
       </c>
       <c r="H183" s="11" t="inlineStr">
         <is>
-          <t>SSI-004412</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="I183" s="11" t="inlineStr">
         <is>
-          <t>Standing settlement instruction identifier.</t>
+          <t>Currency the SSI applies to.</t>
         </is>
       </c>
       <c r="J183" s="24" t="inlineStr"/>
@@ -10538,12 +10538,12 @@
       </c>
       <c r="C184" s="15" t="inlineStr">
         <is>
-          <t>Valid from</t>
+          <t>Is approved</t>
         </is>
       </c>
       <c r="D184" s="23" t="inlineStr">
         <is>
-          <t>valid_from</t>
+          <t>is_approved</t>
         </is>
       </c>
       <c r="E184" s="22" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F184" s="15" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="H184" s="15" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>Effective date of this version.</t>
+          <t>The change went through four-eyes approval.</t>
         </is>
       </c>
       <c r="J184" s="24" t="inlineStr"/>
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C185" s="11" t="inlineStr">
         <is>
-          <t>Valid to</t>
+          <t>SSI ID</t>
         </is>
       </c>
       <c r="D185" s="27" t="inlineStr">
         <is>
-          <t>valid_to</t>
+          <t>ssi_id</t>
         </is>
       </c>
       <c r="E185" s="26" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F185" s="11" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="G185" s="13" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>9999-12-31</t>
+          <t>SSI-004412</t>
         </is>
       </c>
       <c r="I185" s="11" t="inlineStr">
         <is>
-          <t>End of validity.</t>
+          <t>Standing settlement instruction identifier.</t>
         </is>
       </c>
       <c r="J185" s="24" t="inlineStr"/>
@@ -10640,37 +10640,37 @@
       </c>
       <c r="C186" s="15" t="inlineStr">
         <is>
-          <t>SSI change timestamp</t>
+          <t>Valid from</t>
         </is>
       </c>
       <c r="D186" s="23" t="inlineStr">
         <is>
-          <t>ssi_change_timestamp</t>
+          <t>valid_from</t>
         </is>
       </c>
       <c r="E186" s="22" t="inlineStr">
         <is>
-          <t>FACT_SETTLEMENT</t>
+          <t>REF_SSI</t>
         </is>
       </c>
       <c r="F186" s="15" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6) WITH TIME ZONE</t>
-        </is>
-      </c>
-      <c r="G186" s="17" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="G186" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H186" s="15" t="inlineStr">
         <is>
-          <t>2025-08-05T11:20:00+08:00</t>
+          <t>2024-11-02</t>
         </is>
       </c>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>When the SSI was changed.</t>
+          <t>Effective date of this version.</t>
         </is>
       </c>
       <c r="J186" s="24" t="inlineStr"/>
@@ -10691,37 +10691,37 @@
       </c>
       <c r="C187" s="11" t="inlineStr">
         <is>
-          <t>SSI changed by</t>
+          <t>Valid to</t>
         </is>
       </c>
       <c r="D187" s="27" t="inlineStr">
         <is>
-          <t>ssi_changed_by</t>
+          <t>valid_to</t>
         </is>
       </c>
       <c r="E187" s="26" t="inlineStr">
         <is>
-          <t>FACT_SETTLEMENT</t>
+          <t>REF_SSI</t>
         </is>
       </c>
       <c r="F187" s="11" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="G187" s="17" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="G187" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>T54</t>
+          <t>9999-12-31</t>
         </is>
       </c>
       <c r="I187" s="11" t="inlineStr">
         <is>
-          <t>Who changed it.</t>
+          <t>End of validity.</t>
         </is>
       </c>
       <c r="J187" s="24" t="inlineStr"/>
@@ -10742,17 +10742,17 @@
       </c>
       <c r="C188" s="15" t="inlineStr">
         <is>
-          <t>Confirm sent timestamp</t>
+          <t>SSI change timestamp</t>
         </is>
       </c>
       <c r="D188" s="23" t="inlineStr">
         <is>
-          <t>confirm_sent_timestamp</t>
+          <t>ssi_change_timestamp</t>
         </is>
       </c>
       <c r="E188" s="22" t="inlineStr">
         <is>
-          <t>FACT_CONFIRMATION</t>
+          <t>FACT_SETTLEMENT</t>
         </is>
       </c>
       <c r="F188" s="15" t="inlineStr">
@@ -10760,19 +10760,19 @@
           <t>TIMESTAMP(6) WITH TIME ZONE</t>
         </is>
       </c>
-      <c r="G188" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+      <c r="G188" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="H188" s="15" t="inlineStr">
         <is>
-          <t>2025-08-04T18:30:00+08:00</t>
+          <t>2025-08-05T11:20:00+08:00</t>
         </is>
       </c>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>When the confirmation went out.</t>
+          <t>When the SSI was changed.</t>
         </is>
       </c>
       <c r="J188" s="24" t="inlineStr"/>
@@ -10793,17 +10793,17 @@
       </c>
       <c r="C189" s="11" t="inlineStr">
         <is>
-          <t>Confirm status</t>
+          <t>SSI changed by</t>
         </is>
       </c>
       <c r="D189" s="27" t="inlineStr">
         <is>
-          <t>confirm_status</t>
+          <t>ssi_changed_by</t>
         </is>
       </c>
       <c r="E189" s="26" t="inlineStr">
         <is>
-          <t>FACT_CONFIRMATION</t>
+          <t>FACT_SETTLEMENT</t>
         </is>
       </c>
       <c r="F189" s="11" t="inlineStr">
@@ -10811,19 +10811,19 @@
           <t>VARCHAR(20)</t>
         </is>
       </c>
-      <c r="G189" s="13" t="inlineStr">
-        <is>
-          <t>Mandatory</t>
+      <c r="G189" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
         </is>
       </c>
       <c r="H189" s="11" t="inlineStr">
         <is>
-          <t>Matched</t>
+          <t>T54</t>
         </is>
       </c>
       <c r="I189" s="11" t="inlineStr">
         <is>
-          <t>Matching status.</t>
+          <t>Who changed it.</t>
         </is>
       </c>
       <c r="J189" s="24" t="inlineStr"/>
@@ -10844,12 +10844,12 @@
       </c>
       <c r="C190" s="15" t="inlineStr">
         <is>
-          <t>Trade ID</t>
+          <t>Confirm sent timestamp</t>
         </is>
       </c>
       <c r="D190" s="23" t="inlineStr">
         <is>
-          <t>trade_id</t>
+          <t>confirm_sent_timestamp</t>
         </is>
       </c>
       <c r="E190" s="22" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="F190" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>TIMESTAMP(6) WITH TIME ZONE</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H190" s="15" t="inlineStr">
         <is>
-          <t>TRD-051386</t>
+          <t>2025-08-04T18:30:00+08:00</t>
         </is>
       </c>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>Deal confirmed.</t>
+          <t>When the confirmation went out.</t>
         </is>
       </c>
       <c r="J190" s="24" t="inlineStr"/>
@@ -10895,12 +10895,12 @@
       </c>
       <c r="C191" s="11" t="inlineStr">
         <is>
-          <t>Confirm matched timestamp</t>
+          <t>Confirm status</t>
         </is>
       </c>
       <c r="D191" s="27" t="inlineStr">
         <is>
-          <t>confirm_matched_timestamp</t>
+          <t>confirm_status</t>
         </is>
       </c>
       <c r="E191" s="26" t="inlineStr">
@@ -10910,22 +10910,22 @@
       </c>
       <c r="F191" s="11" t="inlineStr">
         <is>
-          <t>TIMESTAMP(6) WITH TIME ZONE</t>
-        </is>
-      </c>
-      <c r="G191" s="17" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="G191" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H191" s="11" t="inlineStr">
         <is>
-          <t>2025-08-05T09:12:00+08:00</t>
+          <t>Matched</t>
         </is>
       </c>
       <c r="I191" s="11" t="inlineStr">
         <is>
-          <t>When it matched.</t>
+          <t>Matching status.</t>
         </is>
       </c>
       <c r="J191" s="24" t="inlineStr"/>
@@ -10946,12 +10946,12 @@
       </c>
       <c r="C192" s="15" t="inlineStr">
         <is>
-          <t>Dispute reason</t>
+          <t>Trade ID</t>
         </is>
       </c>
       <c r="D192" s="23" t="inlineStr">
         <is>
-          <t>dispute_reason</t>
+          <t>trade_id</t>
         </is>
       </c>
       <c r="E192" s="22" t="inlineStr">
@@ -10961,22 +10961,22 @@
       </c>
       <c r="F192" s="15" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="G192" s="17" t="inlineStr">
-        <is>
-          <t>Conditional</t>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="G192" s="13" t="inlineStr">
+        <is>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="H192" s="15" t="inlineStr">
         <is>
-          <t>Rate mismatch</t>
+          <t>TRD-051386</t>
         </is>
       </c>
       <c r="I192" s="15" t="inlineStr">
         <is>
-          <t>Reason a confirmation is disputed.</t>
+          <t>Deal confirmed.</t>
         </is>
       </c>
       <c r="J192" s="24" t="inlineStr"/>
@@ -10986,8 +10986,110 @@
       <c r="N192" s="24" t="inlineStr"/>
       <c r="O192" s="25" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" s="26" t="n">
+        <v>188</v>
+      </c>
+      <c r="B193" s="11" t="inlineStr">
+        <is>
+          <t>Settlement &amp; confirmations</t>
+        </is>
+      </c>
+      <c r="C193" s="11" t="inlineStr">
+        <is>
+          <t>Confirm matched timestamp</t>
+        </is>
+      </c>
+      <c r="D193" s="27" t="inlineStr">
+        <is>
+          <t>confirm_matched_timestamp</t>
+        </is>
+      </c>
+      <c r="E193" s="26" t="inlineStr">
+        <is>
+          <t>FACT_CONFIRMATION</t>
+        </is>
+      </c>
+      <c r="F193" s="11" t="inlineStr">
+        <is>
+          <t>TIMESTAMP(6) WITH TIME ZONE</t>
+        </is>
+      </c>
+      <c r="G193" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="H193" s="11" t="inlineStr">
+        <is>
+          <t>2025-08-05T09:12:00+08:00</t>
+        </is>
+      </c>
+      <c r="I193" s="11" t="inlineStr">
+        <is>
+          <t>When it matched.</t>
+        </is>
+      </c>
+      <c r="J193" s="24" t="inlineStr"/>
+      <c r="K193" s="24" t="inlineStr"/>
+      <c r="L193" s="24" t="inlineStr"/>
+      <c r="M193" s="24" t="inlineStr"/>
+      <c r="N193" s="24" t="inlineStr"/>
+      <c r="O193" s="25" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="22" t="n">
+        <v>189</v>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>Settlement &amp; confirmations</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>Dispute reason</t>
+        </is>
+      </c>
+      <c r="D194" s="23" t="inlineStr">
+        <is>
+          <t>dispute_reason</t>
+        </is>
+      </c>
+      <c r="E194" s="22" t="inlineStr">
+        <is>
+          <t>FACT_CONFIRMATION</t>
+        </is>
+      </c>
+      <c r="F194" s="15" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+      <c r="G194" s="17" t="inlineStr">
+        <is>
+          <t>Conditional</t>
+        </is>
+      </c>
+      <c r="H194" s="15" t="inlineStr">
+        <is>
+          <t>Rate mismatch</t>
+        </is>
+      </c>
+      <c r="I194" s="15" t="inlineStr">
+        <is>
+          <t>Reason a confirmation is disputed.</t>
+        </is>
+      </c>
+      <c r="J194" s="24" t="inlineStr"/>
+      <c r="K194" s="24" t="inlineStr"/>
+      <c r="L194" s="24" t="inlineStr"/>
+      <c r="M194" s="24" t="inlineStr"/>
+      <c r="N194" s="24" t="inlineStr"/>
+      <c r="O194" s="25" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O192"/>
+  <autoFilter ref="A4:O194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Trade-Monitoring-Source-Data-Checklist.xlsx
+++ b/Trade-Monitoring-Source-Data-Checklist.xlsx
@@ -720,7 +720,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>1. Execution timestamp to the second, with a timezone offset — 16 of the 50 rules and three dashboard panels are computed from it, and there is no safe default.
+          <t>1. Execution timestamp to the second, with a timezone offset — 18 of the 58 rules and three dashboard panels are computed from it, and there is no safe default.
 2. Market mid at the moment of execution, not an end-of-day mark. Substituting the close silently changes what every pricing rule tests.
 3. The trader mandate and limit register. In most banks this sits in spreadsheets held by the desk COO rather than in a system, and it is usually the single largest gap.</t>
         </is>
@@ -18527,7 +18527,7 @@
       </c>
       <c r="G106" s="15" t="inlineStr">
         <is>
-          <t>41 of the 50 rules measure against a reference specific to the trader, instrument or product rather than a bank-wide fixed number. That is what this field records. The remaining 9 test against a static list or tolerance.</t>
+          <t>49 of the 58 rules measure against a reference specific to the trader, instrument or product rather than a bank-wide fixed number. That is what this field records. The remaining 9 test against a static list or tolerance.</t>
         </is>
       </c>
     </row>

--- a/Trade-Monitoring-Source-Data-Checklist.xlsx
+++ b/Trade-Monitoring-Source-Data-Checklist.xlsx
@@ -642,6 +642,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -654,6 +655,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -666,6 +668,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -681,6 +684,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -699,6 +703,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
@@ -711,6 +716,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -726,6 +732,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -738,6 +745,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -750,6 +758,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -800,6 +809,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -1233,6 +1243,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
@@ -1295,6 +1306,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -1440,7 +1452,7 @@
       </c>
       <c r="N5" s="20" t="inlineStr">
         <is>
-          <t>J. Tan, FO Tech</t>
+          <t>J. Mochizuki, FO Tech</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -3117,7 +3129,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Nadia Farrell</t>
+          <t>Naomi Fujiwara</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
@@ -3219,7 +3231,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Malcolm Ferris</t>
+          <t>Masato Fujii</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
@@ -11131,6 +11143,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -12208,7 +12221,7 @@
       </c>
       <c r="G28" s="22" t="inlineStr">
         <is>
-          <t>Nadia Farrell</t>
+          <t>Naomi Fujiwara</t>
         </is>
       </c>
       <c r="H28" s="15" t="inlineStr">
@@ -12294,7 +12307,7 @@
       </c>
       <c r="G30" s="22" t="inlineStr">
         <is>
-          <t>Malcolm Ferris</t>
+          <t>Masato Fujii</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
@@ -14924,6 +14937,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
